--- a/out/Attention-mamba2_repeat_5_000001.xlsx
+++ b/out/Attention-mamba2_repeat_5_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.233306561630228</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-2.233306561630228</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.233306561630228</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.633306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.633306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.633306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.633306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.633306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.633306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.633306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-6.522884500527289e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.02808564681070064</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>0.05624624678713619</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.1085088794383322</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.2452518374137715</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>0.03337793958473097</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.2033608363725715</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.006772323509422399</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.1834748228730182</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0</v>
+        <v>0.005863566622783443</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.0001988925241138786</v>
+        <v>0.1884236426376505</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.002863672648104922</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.005425343465515761</v>
+        <v>0.1882820691942722</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.001364083631158653</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.0160108508266625</v>
+        <v>0.188143505866406</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>-0.05416759596207759</v>
+        <v>0.0005656279581166873</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.05437921147487802</v>
+        <v>0.187908437385919</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.0003900958028933744</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.05457112266130117</v>
+        <v>0.1881232567927102</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>-0.0390456213142417</v>
+        <v>0.0001599374780580794</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.09361674397554283</v>
+        <v>0.1880524789126902</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>8.052596622172162e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.09380252257549297</v>
+        <v>0.1880534453850971</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>-0.04617331952757927</v>
+        <v>2.859130153281488e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1399758421030722</v>
+        <v>0.1880298579022884</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>1.332426436274844e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1401538058126791</v>
+        <v>0.1880279254918529</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>-0.000731631602529165</v>
+        <v>4.034747715012475e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.142924140476733</v>
+        <v>0.1880226420301429</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>-7.373950752172664e-07</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1510852387069368</v>
+        <v>0.1880170900940134</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-0.02936622066931296</v>
+        <v>-3.155312586922569e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.170257944068626</v>
+        <v>0.1880114398288601</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>-0.1703908733884182</v>
+        <v>0.1880061985075593</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-0.02824520059180087</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>-0.1986360739802191</v>
+        <v>0.1880009105687088</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>-0.1987652551049039</v>
+        <v>0.1879956387346578</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0005081969917169443</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>-0.183654331904482</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01439376995829394</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>-0.1692605619461883</v>
+        <v>0.1879957184456023</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.006467843873177397</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>-0.1708242174877985</v>
+        <v>0.1879957104745079</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01052433299628456</v>
+        <v>0</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>-0.1562841347841203</v>
+        <v>0.187995869896397</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.003074976038086753</v>
+        <v>0</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>-0.1606929881736918</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005546377220882968</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>-0.1526823471002022</v>
+        <v>0.1879961249714198</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001357716224969524</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>-0.1555230063278217</v>
+        <v>0.1879958778674914</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0005623096158650062</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>-0.1557592010995836</v>
+        <v>0.1879958380120192</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0001875112222506715</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>-0.1559481726398187</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001426269695305353</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>-0.1558512040993606</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>4.316143785167043e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>-0.1559079204751048</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>3.760719725232224e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>-0.1558760205814865</v>
+        <v>0.1879958778674914</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>2.468749723834323e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>-0.1558640071244411</v>
+        <v>0.1879959735206251</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>7.1443818183825e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>-0.1558747977051599</v>
+        <v>0.1879959097518693</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>6.148512719440547e-08</v>
+        <v>0</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>-0.1558816152745525</v>
+        <v>0.187995869896397</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.731987898273899e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>-0.1558871770009844</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>-0.1560810974514636</v>
+        <v>0.1879955988791855</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-0.04800671274998639</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>-0.2040873319357823</v>
+        <v>0.1879955191682407</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>-0.2042686302094048</v>
+        <v>0.1879955669948075</v>
       </c>
     </row>
     <row r="82">
@@ -66123,7 +66123,7 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0.03527173148873241</v>
+        <v>0</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>-0.1333998242097399</v>
+        <v>0.1879956865612245</v>
       </c>
     </row>
     <row r="83">
@@ -66918,7 +66918,7 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0.01526628715108832</v>
+        <v>0</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>-0.1383052126148468</v>
+        <v>0.1879956706190356</v>
       </c>
     </row>
     <row r="84">
@@ -67713,7 +67713,7 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>0.008817873635369258</v>
+        <v>0</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>-0.1360134095232732</v>
+        <v>0.1879956865612245</v>
       </c>
     </row>
     <row r="85">
@@ -68508,7 +68508,7 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0.003816597426610092</v>
+        <v>0</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>-0.1372397648628635</v>
+        <v>0.1879956706190356</v>
       </c>
     </row>
     <row r="86">
@@ -69303,7 +69303,7 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.00294420636050152</v>
+        <v>0</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>-0.1351854116325115</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="87">
@@ -70098,7 +70098,7 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0.001469682430166396</v>
+        <v>0</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>-0.135198990459641</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="88">
@@ -70893,7 +70893,7 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0.0007323412150831982</v>
+        <v>0</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>-0.1352082798732057</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0.0007155224266910483</v>
+        <v>0</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>-0.1345112982122309</v>
+        <v>0.1879958778674914</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.0006052611901096042</v>
+        <v>0</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>-0.1340172816164184</v>
+        <v>0.187996093087042</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0.0002489860971863987</v>
+        <v>0</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>-0.1341249860541712</v>
+        <v>0.187996005405003</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>0.0001083107953771935</v>
+        <v>0</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>-0.1341581701565705</v>
+        <v>0.1879959575784362</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>5.838723595873979e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>-0.1341494348680092</v>
+        <v>0.187996005405003</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>1.35447872162537e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>-0.1341812774926536</v>
+        <v>0.1879958220698303</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>4.431989566918493e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>-0.1341857332734106</v>
+        <v>0.1879958300409247</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>-1.406976918837888e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>-0.1341904573504176</v>
+        <v>0.1879958380120192</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>-2.498695083613412e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>-0.1341953154894616</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>-3.610386157563006e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>-0.1342003208171498</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="99">
@@ -79638,7 +79638,7 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>-4.364539171549108e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>-0.1342051237665167</v>
+        <v>0.1879958858385859</v>
       </c>
     </row>
     <row r="100">
@@ -80433,7 +80433,7 @@
         <v>0</v>
       </c>
       <c r="IY100" t="n">
-        <v>-4.618577352593679e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>-0.1342099336501363</v>
+        <v>0.1879959496073418</v>
       </c>
     </row>
     <row r="101">
@@ -81228,7 +81228,7 @@
         <v>0</v>
       </c>
       <c r="IY101" t="n">
-        <v>-4.507115944527151e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>-0.1342147117832925</v>
+        <v>0.1879960612026642</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>-0.1342146639567257</v>
+        <v>0.1879961090292309</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>-0.134214703812198</v>
+        <v>0.1879960691737586</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>-0.1342147755520482</v>
+        <v>0.1879959974339085</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>-0.1342146559856313</v>
+        <v>0.1879961170003253</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>-0.1342148154075205</v>
+        <v>0.1879959575784362</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>-0.1342150465692598</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>-0.1342150943958267</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>-0.1342150625114487</v>
+        <v>0.1879957104745079</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>-0.1342149987426931</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>-0.1342149987426931</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>-0.1342150784536377</v>
+        <v>0.187995694532319</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>-0.1343724123534663</v>
+        <v>0.1879955749659019</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>-0.1546931296455865</v>
+        <v>0.1879955351104296</v>
       </c>
     </row>
     <row r="115">
@@ -92358,7 +92358,7 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0.0277960679039599</v>
+        <v>0</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>-0.07849991606324096</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="116">
@@ -93153,7 +93153,7 @@
         <v>0</v>
       </c>
       <c r="IY116" t="n">
-        <v>0.03192890711013505</v>
+        <v>0</v>
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>-0.04255487575915502</v>
+        <v>0.1879958140987358</v>
       </c>
     </row>
     <row r="117">
@@ -93948,7 +93948,7 @@
         <v>0</v>
       </c>
       <c r="IY117" t="n">
-        <v>0.01490392272938805</v>
+        <v>0</v>
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>-0.04476333093995077</v>
+        <v>0.1879957981565469</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.006656373496092526</v>
+        <v>0</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>-0.04639748488873197</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.002664249804690448</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>-0.04774582878429326</v>
+        <v>0.1879957343877912</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>-0.049641166825274</v>
+        <v>0.1879956307635633</v>
       </c>
     </row>
     <row r="121">
@@ -97128,21 +97128,21 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>-0.06159708122111943</v>
+        <v>0</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>-0.1121968444414387</v>
+        <v>0.1879955111971462</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>-0.1123605687281441</v>
+        <v>0.1879956307635633</v>
       </c>
     </row>
     <row r="123">
@@ -98718,21 +98718,21 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.0009165803393349051</v>
+        <v>0</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>-0.08910309904147987</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="124">
@@ -99513,7 +99513,7 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>0.03322531068009841</v>
+        <v>0</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>-0.04470727194786701</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>-0.07272399639590667</v>
+        <v>0.1879956546768467</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0.008993160945373278</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>-0.06879724602777731</v>
+        <v>0.1879956626479412</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_5_000001.xlsx
+++ b/out/Attention-mamba2_repeat_5_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4920699483129131</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4920699483129133</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.633306561630228</v>
+        <v>-0.4920699483129133</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.633306561630228</v>
+        <v>-1.165695927975014</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.165695927975014</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.6920699483129134</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4920699483129133</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.633306561630228</v>
+        <v>-0.4920699483129133</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.633306561630228</v>
+        <v>-1.165695927975014</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.165695927975014</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.6920699483129131</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4920699483129133</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.633306561630228</v>
+        <v>0.1815560313491872</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.313807099391461</v>
+        <v>-0.4920699483129133</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.633306561630228</v>
+        <v>-0.4920699483129133</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.633306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.233306561630228</v>
+        <v>-1.365695927975014</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.4920699483129133</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>-6.323940640036016e-05</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0</v>
+        <v>0.0208804616799988</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.313807099391461</v>
+        <v>0.1815560313491872</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.0001988925241138786</v>
+        <v>0.0418240533097519</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.009888248713957342</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.005425343465515761</v>
+        <v>0.04065607516257593</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.004392142230936569</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.0160108508266625</v>
+        <v>0.03952010396294575</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>-0.05416759596207759</v>
+        <v>0.001227847020291219</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.05437921147487802</v>
+        <v>0.03756928576066112</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.001542994621295021</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.05457112266130117</v>
+        <v>0.03942341611205088</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>-0.0390456213142417</v>
+        <v>0.0004929551720415995</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.09361674397554283</v>
+        <v>0.0388625686830699</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.000269983373864672</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.09380252257549297</v>
+        <v>0.03890789473064674</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>-0.04617331952757927</v>
+        <v>5.481900856825949e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1399758421030722</v>
+        <v>0.03874669707932289</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>3.785495067814263e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1401538058126791</v>
+        <v>0.03876727069720975</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>-0.000731631602529165</v>
+        <v>1.527360072946116e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.142924140476733</v>
+        <v>0.03875993827404792</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>3.046351846689906e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1510852387069368</v>
+        <v>0.0387505178341578</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-0.02936622066931296</v>
+        <v>0</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.170257944068626</v>
+        <v>0.03858489228283066</v>
       </c>
     </row>
     <row r="60">
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC60" t="n">
-        <v>-0.1703908733884182</v>
+        <v>0.02255238965867367</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-0.02824520059180087</v>
+        <v>-0.04975632246649229</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC61" t="n">
-        <v>-0.1986360739802191</v>
+        <v>-0.01118208076785062</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC62" t="n">
-        <v>-0.1987652551049039</v>
+        <v>-0.0113365097207533</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0005081969917169443</v>
+        <v>0.000621075375778679</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC63" t="n">
-        <v>-0.183654331904482</v>
+        <v>0.006728468917923747</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01439376995829394</v>
+        <v>0.01719425218838342</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC64" t="n">
-        <v>-0.1692605619461883</v>
+        <v>0.02392276096177904</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.006467843873177397</v>
+        <v>0.007726276519171496</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC65" t="n">
-        <v>-0.1708242174877985</v>
+        <v>0.02205486876584694</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01052433299628456</v>
+        <v>0.01257202686143209</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC66" t="n">
-        <v>-0.1562841347841203</v>
+        <v>0.03942397998483083</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.003074976038086753</v>
+        <v>0.003673346850162153</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC67" t="n">
-        <v>-0.1606929881736918</v>
+        <v>0.03415730598682817</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005546377220882968</v>
+        <v>0.006626107969433742</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC68" t="n">
-        <v>-0.1526823471002022</v>
+        <v>0.04372732247586805</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001357716224969524</v>
+        <v>0.001622880569880624</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC69" t="n">
-        <v>-0.1555230063278217</v>
+        <v>0.04033488606404455</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0005623096158650062</v>
+        <v>0.000672718929644464</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC70" t="n">
-        <v>-0.1557592010995836</v>
+        <v>0.04005370411954564</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0001875112222506715</v>
+        <v>0.000225044856777532</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC71" t="n">
-        <v>-0.1559481726398187</v>
+        <v>0.03982894011589116</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001426269695305353</v>
+        <v>0.0001712863951796197</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC72" t="n">
-        <v>-0.1558512040993606</v>
+        <v>0.03994570422495774</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>4.316143785167043e-05</v>
+        <v>5.244394961637786e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC73" t="n">
-        <v>-0.1559079204751048</v>
+        <v>0.03987894842800487</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>3.760719725232224e-05</v>
+        <v>4.593821347484335e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.01844396865081287</v>
       </c>
       <c r="JC74" t="n">
-        <v>-0.1558760205814865</v>
+        <v>0.03991806338462117</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>2.468749723834323e-05</v>
+        <v>3.069171016295198e-05</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.233306561630228</v>
+        <v>-0.01844396865081287</v>
       </c>
       <c r="JC75" t="n">
-        <v>-0.1558640071244411</v>
+        <v>0.03993340276685229</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>7.1443818183825e-06</v>
+        <v>9.303383030539388e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.7138070993914607</v>
+        <v>-0.01844396865081287</v>
       </c>
       <c r="JC76" t="n">
-        <v>-0.1558747977051599</v>
+        <v>0.03992151898080565</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>6.148512719440547e-08</v>
+        <v>1.211822656102225e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC77" t="n">
-        <v>-0.1558816152745525</v>
+        <v>0.03991433724099432</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.731987898273899e-06</v>
+        <v>-2.319622061596426e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.313807099391461</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC78" t="n">
-        <v>-0.1558871770009844</v>
+        <v>0.03990867773035355</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC79" t="n">
-        <v>-0.1560810974514636</v>
+        <v>0.03971579084437678</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-0.04800671274998639</v>
+        <v>-0.04762287855792017</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC80" t="n">
-        <v>-0.2040873319357823</v>
+        <v>-0.007906529736931086</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC81" t="n">
-        <v>-0.2042686302094048</v>
+        <v>-0.008088260067483876</v>
       </c>
     </row>
     <row r="82">
@@ -66123,7 +66123,7 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0.03527173148873241</v>
+        <v>0.03535572929076491</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC82" t="n">
-        <v>-0.1333998242097399</v>
+        <v>0.06294943589022289</v>
       </c>
     </row>
     <row r="83">
@@ -66918,7 +66918,7 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0.01526628715108832</v>
+        <v>0.01530269430106673</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC83" t="n">
-        <v>-0.1383052126148468</v>
+        <v>0.05803234908002242</v>
       </c>
     </row>
     <row r="84">
@@ -67713,7 +67713,7 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>0.008817873635369258</v>
+        <v>0.008838961941098148</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.313807099391461</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC84" t="n">
-        <v>-0.1360134095232732</v>
+        <v>0.0603296171321813</v>
       </c>
     </row>
     <row r="85">
@@ -68508,7 +68508,7 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0.003816597426610092</v>
+        <v>0.003825622297590656</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.8551820110112874</v>
       </c>
       <c r="JC85" t="n">
-        <v>-0.1372397648628635</v>
+        <v>0.05910034596406925</v>
       </c>
     </row>
     <row r="86">
@@ -69303,7 +69303,7 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.00294420636050152</v>
+        <v>0.002951338852908816</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC86" t="n">
-        <v>-0.1351854116325115</v>
+        <v>0.06115962369366293</v>
       </c>
     </row>
     <row r="87">
@@ -70098,7 +70098,7 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0.001469682430166396</v>
+        <v>0.001473169426454408</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC87" t="n">
-        <v>-0.135198990459641</v>
+        <v>0.06114602458125865</v>
       </c>
     </row>
     <row r="88">
@@ -70893,7 +70893,7 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0.0007323412150831982</v>
+        <v>0.000734084713227204</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC88" t="n">
-        <v>-0.1352082798732057</v>
+        <v>0.0611367250250564</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0.0007155224266910483</v>
+        <v>0.0007170712711164375</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC89" t="n">
-        <v>-0.1345112982122309</v>
+        <v>0.06183536712577916</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.0006052611901096042</v>
+        <v>0.000606835380625794</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC90" t="n">
-        <v>-0.1340172816164184</v>
+        <v>0.0623306709527073</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0.0002489860971863987</v>
+        <v>0.0002498604038892779</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC91" t="n">
-        <v>-0.1341249860541712</v>
+        <v>0.06222270095514925</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC92" t="n">
-        <v>-0.1341581701565705</v>
+        <v>0.06218946902618325</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>5.838723595873979e-05</v>
+        <v>5.882438931017937e-05</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC93" t="n">
-        <v>-0.1341494348680092</v>
+        <v>0.0621982508844675</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC94" t="n">
-        <v>-0.1341812774926536</v>
+        <v>0.06216640825982299</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC95" t="n">
-        <v>-0.1341857332734106</v>
+        <v>0.06216195247906586</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC96" t="n">
-        <v>-0.1341904573504176</v>
+        <v>0.06215722840205906</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC97" t="n">
-        <v>-0.1341953154894616</v>
+        <v>0.06215237026301492</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC98" t="n">
-        <v>-0.1342003208171498</v>
+        <v>0.06214736493532663</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC99" t="n">
-        <v>-0.1342051237665167</v>
+        <v>0.06214256198595976</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC100" t="n">
-        <v>-0.1342099336501363</v>
+        <v>0.06213775210234011</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC101" t="n">
-        <v>-0.1342147117832925</v>
+        <v>0.06213297396918386</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC102" t="n">
-        <v>-0.1342146639567257</v>
+        <v>0.06213302179575059</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC103" t="n">
-        <v>-0.134214703812198</v>
+        <v>0.06213298194027832</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC104" t="n">
-        <v>-0.1342147755520482</v>
+        <v>0.06213291020042822</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC105" t="n">
-        <v>-0.1342146559856313</v>
+        <v>0.06213302976684505</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC106" t="n">
-        <v>-0.1342148154075205</v>
+        <v>0.06213287034495594</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC107" t="n">
-        <v>-0.1342150465692598</v>
+        <v>0.06213263918321649</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC108" t="n">
-        <v>-0.1342150943958267</v>
+        <v>0.06213259135664976</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC109" t="n">
-        <v>-0.1342150625114487</v>
+        <v>0.06213262324102758</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC110" t="n">
-        <v>-0.1342149987426931</v>
+        <v>0.06213268700978323</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC111" t="n">
-        <v>-0.1342149987426931</v>
+        <v>0.06213268700978323</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC112" t="n">
-        <v>-0.1342150784536377</v>
+        <v>0.06213260729883868</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC113" t="n">
-        <v>-0.1343724123534663</v>
+        <v>0.06194673633821565</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC114" t="n">
-        <v>-0.1546931296455865</v>
+        <v>0.03793832174600358</v>
       </c>
     </row>
     <row r="115">
@@ -92358,7 +92358,7 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0.0277960679039599</v>
+        <v>0.03287736922474094</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC115" t="n">
-        <v>-0.07849991606324096</v>
+        <v>0.1280339535704881</v>
       </c>
     </row>
     <row r="116">
@@ -93153,7 +93153,7 @@
         <v>0</v>
       </c>
       <c r="IY116" t="n">
-        <v>0.03192890711013505</v>
+        <v>0.03775974679583912</v>
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC116" t="n">
-        <v>-0.04255487575915502</v>
+        <v>0.1705376888190408</v>
       </c>
     </row>
     <row r="117">
@@ -93948,7 +93948,7 @@
         <v>0</v>
       </c>
       <c r="IY117" t="n">
-        <v>0.01490392272938805</v>
+        <v>0.01762558448327354</v>
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC117" t="n">
-        <v>-0.04476333093995077</v>
+        <v>0.1679262792795093</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.006656373496092526</v>
+        <v>0.007872165415879697</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC118" t="n">
-        <v>-0.04639748488873197</v>
+        <v>0.1659939450369927</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.002664249804690448</v>
+        <v>0.003151814565643753</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC119" t="n">
-        <v>-0.04774582878429326</v>
+        <v>0.1644004885222055</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC120" t="n">
-        <v>-0.049641166825274</v>
+        <v>0.162160213228618</v>
       </c>
     </row>
     <row r="121">
@@ -97128,7 +97128,7 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>-0.06159708122111943</v>
+        <v>-0.07249678447010979</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC121" t="n">
-        <v>-0.1121968444414387</v>
+        <v>0.08852929285209765</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC122" t="n">
-        <v>-0.1123605687281441</v>
+        <v>0.08833609834851301</v>
       </c>
     </row>
     <row r="123">
@@ -98718,7 +98718,7 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.0009165803393349051</v>
+        <v>0.001109229526438741</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC123" t="n">
-        <v>-0.08910309904147987</v>
+        <v>0.1157801659863242</v>
       </c>
     </row>
     <row r="124">
@@ -99513,7 +99513,7 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>0.03322531068009841</v>
+        <v>0.03916518440665168</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC124" t="n">
-        <v>-0.04470727194786701</v>
+        <v>0.1681127694486617</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC125" t="n">
-        <v>-0.07272399639590667</v>
+        <v>0.1350876467646737</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0.008993160945373278</v>
+        <v>0.010598498034097</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7138070993914607</v>
+        <v>0.6551820110112874</v>
       </c>
       <c r="JC126" t="n">
-        <v>-0.06879724602777731</v>
+        <v>0.1397133599917879</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_5_000001.xlsx
+++ b/out/Attention-mamba2_repeat_5_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.1630008220672607</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.3507346510887146</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.05626434832811356</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.04245425015687943</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.1399314403533936</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.3215298652648926</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0458625927567482</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.06939993053674698</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.1056206896901131</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.02009668946266174</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.08724873512983322</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.05453582853078842</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.1687269508838654</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.4100927412509918</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.366508275270462</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.2659043073654175</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.2792425751686096</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.2951205670833588</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.2575042545795441</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.4920699483129131</v>
+        <v>0.16</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.007927216589450836</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4920699483129133</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.02741173654794693</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4920699483129133</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.06514293700456619</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.165695927975014</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.3177480101585388</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.165695927975014</v>
+        <v>0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.2949035167694092</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.2444078028202057</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.2394499778747559</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.04456856101751328</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.6920699483129134</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.01744113489985466</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.4920699483129133</v>
+        <v>0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.1654100716114044</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4920699483129133</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.2741400599479675</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.165695927975014</v>
+        <v>0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.1474696099758148</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.165695927975014</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.2677579820156097</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6920699483129131</v>
+        <v>0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.0002756491303443909</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4920699483129133</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.007506802678108215</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.1815560313491872</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.01038471609354019</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.4920699483129133</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.02505169808864594</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4920699483129133</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.2292347550392151</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.2539606392383575</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.2808872759342194</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.06782939285039902</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.3</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.0185871347784996</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.365695927975014</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.007247291505336761</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.365695927975014</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-0.0001702408744366839</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.07330077777373428</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.04564573615789413</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.365695927975014</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>0.1467971759432526</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.2831996698953014</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.09579824656248093</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.365695927975014</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.6400831868157596</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>0.08711329698371349</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.09322797507047653</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.365695927975014</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.5307526231656382</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.01767614252776867</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.04319295287132263</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4920699483129133</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-6.323940640036016e-05</v>
+        <v>0.4788543111816319</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0208804616799988</v>
+        <v>0.01530832500785563</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.01620198786258698</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.1815560313491872</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.0418240533097519</v>
+        <v>0.4917752774562403</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009888248713957342</v>
+        <v>0.00748238961545394</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.009481832385063171</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.04065607516257593</v>
+        <v>0.4914138391048955</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004392142230936569</v>
+        <v>0.003568381776201306</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.05957917869091034</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.03952010396294575</v>
+        <v>0.4910602829844139</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001227847020291219</v>
+        <v>0.001483643082930753</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.07320597767829895</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.03756928576066112</v>
+        <v>0.4904549732263382</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001542994621295021</v>
+        <v>0.001026724782164925</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.1062522009015083</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.03942341611205088</v>
+        <v>0.4910236470363983</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0004929551720415995</v>
+        <v>0.0004260280188314653</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.02912706136703491</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.0388625686830699</v>
+        <v>0.4908470842272644</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.000269983373864672</v>
+        <v>0.0002181693181098049</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.01312138885259628</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.03890789473064674</v>
+        <v>0.4908576145057606</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>5.481900856825949e-05</v>
+        <v>8.265230243718883e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.08919908851385117</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.03874669707932289</v>
+        <v>0.4908043437054495</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>3.785495067814263e-05</v>
+        <v>4.310119395221467e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.08303774148225784</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.03876727069720975</v>
+        <v>0.4908072705833183</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.527360072946116e-05</v>
+        <v>1.871621275190775e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.03490470349788666</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.8551820110112874</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.03875993827404792</v>
+        <v>0.4908015474204531</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>3.046351846689906e-06</v>
+        <v>6.189337927554673e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.03236034139990807</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.0387505178341578</v>
+        <v>0.4907951822846045</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>-3.882814673064221e-07</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.03673750162124634</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.03858489228283066</v>
+        <v>0.4907886642314969</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-2.932986608081494e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.04842878878116608</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.02255238965867367</v>
+        <v>0.4907831326680945</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-0.04975632246649229</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.09297546744346619</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>-0.01118208076785062</v>
+        <v>0.4907775558109437</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.05799038708209991</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>-0.0113365097207533</v>
+        <v>0.4907721484682867</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.000621075375778679</v>
+        <v>-4.777674021158921e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.08680780977010727</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.006728468917923747</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01719425218838342</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.05726892501115799</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.02392276096177904</v>
+        <v>0.4907672671700376</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007726276519171496</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.08311814814805984</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.02205486876584694</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01257202686143209</v>
+        <v>0</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.1142096668481827</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.03942397998483083</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.003673346850162153</v>
+        <v>0</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.04028256610035896</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.03415730598682817</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006626107969433742</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.07759370654821396</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.04372732247586805</v>
+        <v>0.4907676736958551</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001622880569880624</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.1021324098110199</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.16</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.04033488606404455</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.000672718929644464</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.07984396070241928</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.16</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.04005370411954564</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.000225044856777532</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.04345263913273811</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.03982894011589116</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001712863951796197</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.03716197237372398</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.16</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.03994570422495774</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.244394961637786e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.07783162593841553</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.03987894842800487</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>4.593821347484335e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.05953934788703918</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.01844396865081287</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.03991806338462117</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>3.069171016295198e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.0105636939406395</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.01844396865081287</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.03993340276685229</v>
+        <v>0.4907675222450604</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>9.303383030539388e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.04973021522164345</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.01844396865081287</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.03992151898080565</v>
+        <v>0.4907674584763045</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>1.211822656102225e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.04807679355144501</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.03991433724099432</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.319622061596426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.07966762036085129</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.03990867773035355</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.04630948603153229</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.8551820110112874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.03971579084437678</v>
+        <v>0.4907671476036208</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-0.04762287855792017</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.02660415321588516</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.8551820110112874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>-0.007906529736931086</v>
+        <v>0.490767067892676</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.02076534926891327</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.8551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>-0.008088260067483876</v>
+        <v>0.4907671157192427</v>
       </c>
     </row>
     <row r="82">
@@ -66123,7 +66123,7 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0.03535572929076491</v>
+        <v>0</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.02496480941772461</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.8551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.06294943589022289</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="83">
@@ -66918,7 +66918,7 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0.01530269430106673</v>
+        <v>0</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.0264711007475853</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.8551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.05803234908002242</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="84">
@@ -67713,7 +67713,7 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>0.008838961941098148</v>
+        <v>0</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.03002841770648956</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.8551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.0603296171321813</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="85">
@@ -68508,7 +68508,7 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0.003825622297590656</v>
+        <v>0</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.02993779629468918</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.8551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.05910034596406925</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="86">
@@ -69303,7 +69303,7 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.002951338852908816</v>
+        <v>0</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.02529224008321762</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.06115962369366293</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="87">
@@ -70098,7 +70098,7 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0.001473169426454408</v>
+        <v>0</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.04300627484917641</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.16</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.06114602458125865</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="88">
@@ -70893,7 +70893,7 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0.000734084713227204</v>
+        <v>0</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.07062272727489471</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.0611367250250564</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0.0007170712711164375</v>
+        <v>0</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.06150511652231216</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.06183536712577916</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.000606835380625794</v>
+        <v>0</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.04754089936614037</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.16</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.0623306709527073</v>
+        <v>0.4907676418114773</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0.0002498604038892779</v>
+        <v>0</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.04368973895907402</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.06222270095514925</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>0.0001083107953771935</v>
+        <v>0</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.03459417819976807</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.06218946902618325</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>5.882438931017937e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.03353983163833618</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.0621982508844675</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>1.35447872162537e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.02640362828969955</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.06216640825982299</v>
+        <v>0.4907673707942655</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>4.431989566918493e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.024479690939188</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.06216195247906586</v>
+        <v>0.49076737876536</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>-1.406976918837888e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.02312403917312622</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.06215722840205906</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>-2.498695083613412e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.01935194060206413</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.06215237026301492</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>-3.610386157563006e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.03819186985492706</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.06214736493532663</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="99">
@@ -79638,7 +79638,7 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>-4.364539171549108e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.08164631575345993</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.06214256198595976</v>
+        <v>0.4907674345630212</v>
       </c>
     </row>
     <row r="100">
@@ -80433,7 +80433,7 @@
         <v>0</v>
       </c>
       <c r="IY100" t="n">
-        <v>-4.618577352593679e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.05328376218676567</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.06213775210234011</v>
+        <v>0.4907674983317771</v>
       </c>
     </row>
     <row r="101">
@@ -81228,7 +81228,7 @@
         <v>0</v>
       </c>
       <c r="IY101" t="n">
-        <v>-4.507115944527151e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.07202840596437454</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.06213297396918386</v>
+        <v>0.4907676099270994</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.03892375528812408</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.06213302179575059</v>
+        <v>0.4907676577536662</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.03908820450305939</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.06213298194027832</v>
+        <v>0.4907676178981939</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.0467676967382431</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.06213291020042822</v>
+        <v>0.4907675461583438</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.08940628170967102</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.06213302976684505</v>
+        <v>0.4907676657247606</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.07599252462387085</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.06213287034495594</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.04776977002620697</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.06213263918321649</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.02866890281438828</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.06213259135664976</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.0271771103143692</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.06213262324102758</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.02389248460531235</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.06213268700978323</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.02085399627685547</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.06213268700978323</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.02160917967557907</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.06213260729883868</v>
+        <v>0.4907672432567542</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.02183283120393753</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.06194673633821565</v>
+        <v>0.4907671236903371</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.02668659016489983</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.03793832174600358</v>
+        <v>0.4907670838348649</v>
       </c>
     </row>
     <row r="115">
@@ -92358,7 +92358,7 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0.03287736922474094</v>
+        <v>0</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.02561872452497482</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1280339535704881</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="116">
@@ -93153,7 +93153,7 @@
         <v>0</v>
       </c>
       <c r="IY116" t="n">
-        <v>0.03775974679583912</v>
+        <v>0</v>
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.02126115560531616</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1705376888190408</v>
+        <v>0.4907673628231711</v>
       </c>
     </row>
     <row r="117">
@@ -93948,7 +93948,7 @@
         <v>0</v>
       </c>
       <c r="IY117" t="n">
-        <v>0.01762558448327354</v>
+        <v>0</v>
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.01926096528768539</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.6551820110112874</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1679262792795093</v>
+        <v>0.4907673468809822</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.007872165415879697</v>
+        <v>0</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.02161673456430435</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1659939450369927</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.003151814565643753</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.03592761233448982</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1644004885222055</v>
+        <v>0.4907672831122265</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.08934810757637024</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.162160213228618</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="121">
@@ -97128,21 +97128,21 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>-0.07249678447010979</v>
+        <v>0</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.09537696838378906</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.08852929285209765</v>
+        <v>0.4907670599215815</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.04264087975025177</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.08833609834851301</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="123">
@@ -98718,21 +98718,21 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.001109229526438741</v>
+        <v>0</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.02859243005514145</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1157801659863242</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="124">
@@ -99513,7 +99513,7 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>0.03916518440665168</v>
+        <v>0</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.02647243067622185</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1681127694486617</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.03744809702038765</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.3700000000000002</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1350876467646737</v>
+        <v>0.4907672034012819</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0.010598498034097</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.1115025132894516</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.6551820110112874</v>
+        <v>0.5800000000000003</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1397133599917879</v>
+        <v>0.4907672113723764</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_5_000001.xlsx
+++ b/out/Attention-mamba2_repeat_5_000001.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.1630008220672607</v>
+        <v>-0.1630007326602936</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.3507346510887146</v>
+        <v>-0.3507343530654907</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.05626434832811356</v>
+        <v>-0.05626418441534042</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.04245425015687943</v>
+        <v>-0.04245411604642868</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.1399314403533936</v>
+        <v>-0.1399312019348145</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.3215298652648926</v>
+        <v>-0.3215293884277344</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.0458625927567482</v>
+        <v>-0.04586236923933029</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.06939993053674698</v>
+        <v>-0.06939973682165146</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.8599999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.1056206896901131</v>
+        <v>-0.1056204065680504</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.8599999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.02009668946266174</v>
+        <v>-0.02009651809930801</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.2599999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.08724873512983322</v>
+        <v>-0.08724860101938248</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.2599999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.05453582853078842</v>
+        <v>-0.05453572422266006</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.2599999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.1687269508838654</v>
+        <v>-0.168726772069931</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.3999999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.4100927412509918</v>
+        <v>-0.4100924432277679</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.9999999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.366508275270462</v>
+        <v>-0.3665079772472382</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.9999999999999998</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.2659043073654175</v>
+        <v>-0.2659042477607727</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.9999999999999998</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.2792425751686096</v>
+        <v>-0.2792425155639648</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.9999999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.2951205670833588</v>
+        <v>-0.2951204180717468</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.1199999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.2575042545795441</v>
+        <v>-0.2575042247772217</v>
       </c>
       <c r="JB20" t="n">
         <v>0.16</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.007927216589450836</v>
+        <v>0.007927320897579193</v>
       </c>
       <c r="JB21" t="n">
         <v>0.4399999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.02741173654794693</v>
+        <v>-0.0274115726351738</v>
       </c>
       <c r="JB22" t="n">
         <v>0.4399999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.06514293700456619</v>
+        <v>-0.06514275819063187</v>
       </c>
       <c r="JB23" t="n">
         <v>0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.3177480101585388</v>
+        <v>-0.317747950553894</v>
       </c>
       <c r="JB24" t="n">
         <v>0.16</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.2949035167694092</v>
+        <v>-0.2949034571647644</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.1199999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.2444078028202057</v>
+        <v>-0.2444077730178833</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.7199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.2394499778747559</v>
+        <v>-0.2394498884677887</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.4399999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.04456856101751328</v>
+        <v>-0.04456941783428192</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.3</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.01744113489985466</v>
+        <v>0.01744119822978973</v>
       </c>
       <c r="JB29" t="n">
         <v>0.3</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.1654100716114044</v>
+        <v>-0.1654163599014282</v>
       </c>
       <c r="JB30" t="n">
         <v>0.5799999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.2741400599479675</v>
+        <v>-0.2741399705410004</v>
       </c>
       <c r="JB31" t="n">
         <v>0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.1474696099758148</v>
+        <v>-0.1474750936031342</v>
       </c>
       <c r="JB32" t="n">
         <v>0.1600000000000001</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.2677579820156097</v>
+        <v>-0.2677577137947083</v>
       </c>
       <c r="JB33" t="n">
         <v>0.3</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.0002756491303443909</v>
+        <v>0.0002757906913757324</v>
       </c>
       <c r="JB34" t="n">
         <v>0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.007506802678108215</v>
+        <v>-0.007506661117076874</v>
       </c>
       <c r="JB35" t="n">
         <v>0.5799999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.01038471609354019</v>
+        <v>0.01038484275341034</v>
       </c>
       <c r="JB36" t="n">
         <v>0.5799999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.02505169808864594</v>
+        <v>-0.02505152672529221</v>
       </c>
       <c r="JB37" t="n">
         <v>0.4399999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.2292347550392151</v>
+        <v>-0.2292346954345703</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.4399999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.2539606392383575</v>
+        <v>-0.2539605498313904</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.5799999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.2808872759342194</v>
+        <v>-0.2808871567249298</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.5799999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.06782939285039902</v>
+        <v>-0.06782928854227066</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.3</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.0185871347784996</v>
+        <v>-0.01858700066804886</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.02000000000000007</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.007247291505336761</v>
+        <v>-0.00724724680185318</v>
       </c>
       <c r="JB43" t="n">
         <v>0.8599999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.04564573615789413</v>
+        <v>-0.04564554244279861</v>
       </c>
       <c r="JB44" t="n">
         <v>0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.09579824656248093</v>
+        <v>-0.09579838067293167</v>
       </c>
       <c r="JB45" t="n">
         <v>0.7199999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.09322797507047653</v>
+        <v>-0.09322825819253922</v>
       </c>
       <c r="JB46" t="n">
         <v>0.7199999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.04319295287132263</v>
+        <v>-0.04319324344396591</v>
       </c>
       <c r="JB47" t="n">
         <v>0.7199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.01620198786258698</v>
+        <v>0.01620205491781235</v>
       </c>
       <c r="JB48" t="n">
         <v>0.7199999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.009481832385063171</v>
+        <v>0.00948178768157959</v>
       </c>
       <c r="JB49" t="n">
         <v>0.8599999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.05957917869091034</v>
+        <v>0.05957907438278198</v>
       </c>
       <c r="JB50" t="n">
         <v>0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.07320597767829895</v>
+        <v>0.07320591807365417</v>
       </c>
       <c r="JB51" t="n">
         <v>0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.1062522009015083</v>
+        <v>0.1062521636486053</v>
       </c>
       <c r="JB52" t="n">
         <v>0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.02912706136703491</v>
+        <v>0.02912692353129387</v>
       </c>
       <c r="JB53" t="n">
         <v>0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.01312138885259628</v>
+        <v>0.01312120631337166</v>
       </c>
       <c r="JB54" t="n">
         <v>0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.08919908851385117</v>
+        <v>0.08919894695281982</v>
       </c>
       <c r="JB55" t="n">
         <v>0.8599999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.08303774148225784</v>
+        <v>0.08303770422935486</v>
       </c>
       <c r="JB56" t="n">
         <v>0.8599999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.03490470349788666</v>
+        <v>0.03490471839904785</v>
       </c>
       <c r="JB57" t="n">
         <v>0.2599999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.03236034139990807</v>
+        <v>0.03236033767461777</v>
       </c>
       <c r="JB58" t="n">
         <v>0.1199999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.03673750162124634</v>
+        <v>0.03673751652240753</v>
       </c>
       <c r="JB59" t="n">
         <v>0.1199999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.04842878878116608</v>
+        <v>0.0484287366271019</v>
       </c>
       <c r="JB60" t="n">
         <v>0.2599999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.09297546744346619</v>
+        <v>0.09297525137662888</v>
       </c>
       <c r="JB61" t="n">
         <v>0.2599999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.05799038708209991</v>
+        <v>0.0579904280602932</v>
       </c>
       <c r="JB62" t="n">
         <v>0.2599999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.08680780977010727</v>
+        <v>0.08680780231952667</v>
       </c>
       <c r="JB63" t="n">
         <v>0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.05726892501115799</v>
+        <v>0.05726891756057739</v>
       </c>
       <c r="JB64" t="n">
         <v>0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.08311814814805984</v>
+        <v>0.08311809599399567</v>
       </c>
       <c r="JB65" t="n">
         <v>0.8599999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.1142096668481827</v>
+        <v>0.1142096295952797</v>
       </c>
       <c r="JB66" t="n">
         <v>0.7199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.04028256610035896</v>
+        <v>0.04028240963816643</v>
       </c>
       <c r="JB67" t="n">
         <v>0.1199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.07759370654821396</v>
+        <v>0.07759355753660202</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.02000000000000007</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.1021324098110199</v>
+        <v>0.1021322682499886</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.16</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.07984396070241928</v>
+        <v>0.07984387874603271</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.16</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.04345263913273811</v>
+        <v>0.04345262795686722</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.02000000000000007</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.03716197237372398</v>
+        <v>0.0371619239449501</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.16</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.07783162593841553</v>
+        <v>0.07783158123493195</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.3</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.05953934788703918</v>
+        <v>0.0595393106341362</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.3</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.0105636939406395</v>
+        <v>-0.0105639323592186</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.4399999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.04973021522164345</v>
+        <v>0.0497300885617733</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.4399999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.04807679355144501</v>
+        <v>0.0480768159031868</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.5799999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.07966762036085129</v>
+        <v>0.07966760545969009</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.5799999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.04630948603153229</v>
+        <v>0.04630949720740318</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.7199999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.02660415321588516</v>
+        <v>0.02660413831472397</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.7199999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.02496480941772461</v>
+        <v>0.0249648243188858</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.0264711007475853</v>
+        <v>0.02647117152810097</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.9999999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.03002841770648956</v>
+        <v>0.03002835065126419</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.9999999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.02993779629468918</v>
+        <v>0.02993778884410858</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.9999999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.02529224008321762</v>
+        <v>0.02529223263263702</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.7199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.04300627484917641</v>
+        <v>0.04300624877214432</v>
       </c>
       <c r="JB87" t="n">
         <v>0.16</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.07062272727489471</v>
+        <v>0.07062266767024994</v>
       </c>
       <c r="JB88" t="n">
         <v>0.1600000000000001</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.06150511652231216</v>
+        <v>0.06150506809353828</v>
       </c>
       <c r="JB89" t="n">
         <v>0.1600000000000001</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.04754089936614037</v>
+        <v>0.04754085466265678</v>
       </c>
       <c r="JB90" t="n">
         <v>0.16</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.04368973895907402</v>
+        <v>0.04368975758552551</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.1199999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.03459417819976807</v>
+        <v>0.0345940887928009</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.9999999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.03353983163833618</v>
+        <v>0.03353969007730484</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.9999999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.02640362828969955</v>
+        <v>0.02640361338853836</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.9999999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.024479690939188</v>
+        <v>0.0244797095656395</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.9999999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.02312403917312622</v>
+        <v>0.02312410250306129</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.8599999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.01935194060206413</v>
+        <v>0.01935192197561264</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.5799999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.03819186985492706</v>
+        <v>0.03819185495376587</v>
       </c>
       <c r="JB98" t="n">
         <v>0.3</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.08164631575345993</v>
+        <v>0.08164625614881516</v>
       </c>
       <c r="JB99" t="n">
         <v>0.5799999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.05328376218676567</v>
+        <v>0.05328356474637985</v>
       </c>
       <c r="JB100" t="n">
         <v>0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.07202840596437454</v>
+        <v>0.07202772796154022</v>
       </c>
       <c r="JB101" t="n">
         <v>0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.03892375528812408</v>
+        <v>0.03892374411225319</v>
       </c>
       <c r="JB102" t="n">
         <v>0.5799999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.03908820450305939</v>
+        <v>0.03908814862370491</v>
       </c>
       <c r="JB103" t="n">
         <v>0.5799999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.0467676967382431</v>
+        <v>0.04676748439669609</v>
       </c>
       <c r="JB104" t="n">
         <v>0.5799999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.08940628170967102</v>
+        <v>0.08940593153238297</v>
       </c>
       <c r="JB105" t="n">
         <v>0.5799999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.07599252462387085</v>
+        <v>0.07599245011806488</v>
       </c>
       <c r="JB106" t="n">
         <v>0.4399999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.04776977002620697</v>
+        <v>0.04776976257562637</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.3</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.02866890281438828</v>
+        <v>0.0286688357591629</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.5799999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.0271771103143692</v>
+        <v>0.02717714011669159</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.8599999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.02389248460531235</v>
+        <v>0.02389247715473175</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.02085399627685547</v>
+        <v>0.02085399255156517</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.02160917967557907</v>
+        <v>0.02160924673080444</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.02183283120393753</v>
+        <v>0.02183283865451813</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.02668659016489983</v>
+        <v>0.02668661624193192</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.02561872452497482</v>
+        <v>0.02561875432729721</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.9999999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.02126115560531616</v>
+        <v>0.02126111090183258</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.9999999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.01926096528768539</v>
+        <v>0.01926100626587868</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.8599999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.02161673456430435</v>
+        <v>0.02161674201488495</v>
       </c>
       <c r="JB118" t="n">
         <v>0.02000000000000007</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.03592761233448982</v>
+        <v>0.03592761605978012</v>
       </c>
       <c r="JB119" t="n">
         <v>0.3</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.08934810757637024</v>
+        <v>0.08934894204139709</v>
       </c>
       <c r="JB120" t="n">
         <v>0.4399999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.09537696838378906</v>
+        <v>0.09537695348262787</v>
       </c>
       <c r="JB121" t="n">
         <v>0.4399999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.04264087975025177</v>
+        <v>0.04264091327786446</v>
       </c>
       <c r="JB122" t="n">
         <v>0.3</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.02859243005514145</v>
+        <v>0.02859237045049667</v>
       </c>
       <c r="JB123" t="n">
         <v>0.16</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.02647243067622185</v>
+        <v>0.02647244185209274</v>
       </c>
       <c r="JB124" t="n">
         <v>0.16</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.03744809702038765</v>
+        <v>0.03744808584451675</v>
       </c>
       <c r="JB125" t="n">
         <v>0.3700000000000002</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.1115025132894516</v>
+        <v>0.1115024536848068</v>
       </c>
       <c r="JB126" t="n">
         <v>0.5800000000000003</v>
